--- a/光伏配储项目/电价数据/2026/罗洞站.xlsx
+++ b/光伏配储项目/电价数据/2026/罗洞站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51183</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75785</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5989</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51605</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12808</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10422</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10792</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13055</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04898</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10755</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15673</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20315</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09128</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10094</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04505</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15238</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21668</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25468</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.18357</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.02363</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.54843</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14295</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21247</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56398</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.32898</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6155700000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44664</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46351</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57762</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47369</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63474</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82037</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63951</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6518400000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7934</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14668</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42896</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68477</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6002000000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.82016</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6653300000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.68145</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65079</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6205700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48133</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42616</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80423</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.55468</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8669199999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53661</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51801</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5086499999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.4977200000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59975</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7535700000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52111</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17074</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06092</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50238</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76702</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.16527</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.41657</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.79601</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.53884</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13044</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.51315</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26471</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.13541</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.46654</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.29439</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43053</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.63914</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.78484</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.23902</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7900700000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73902</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.66471</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.60493</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77435</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.56608</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45509</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.08269</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.67645</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3347</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51752</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52399</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.47716</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47579</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48589</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16323</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5373300000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.21781</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5856</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.9181699999999999</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56237</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.63863</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.70623</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57723</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49624</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52547</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.48278</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47272</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34231</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.37392</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.26427</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.09659999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17393</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.17763</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21775</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06668</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24226</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21654</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23635</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20008</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12504</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.21955</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.26843</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6725800000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4724100000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29912</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41584</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03886999999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04939</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04075</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04525999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04238</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03623</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04717</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04770000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04677000000000001</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21833</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03927000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04516</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00305</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01222</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15506</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11281</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46729</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67674</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09786</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00471</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04463</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04776</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14285</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33536</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31743</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17241</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17095</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15945</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22657</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15635</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78107</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91522</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86524</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29789</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89027</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6322000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18985</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8701100000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53899</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33362</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03485</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53351</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7932400000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5293300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7752599999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77934</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87705</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87505</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49526</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40267</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20977</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62461</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53903</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49852</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5853700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6014400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6616599999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5822999999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87787</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62778</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8746499999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.85722</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8650399999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46003</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35324</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91501</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16657</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19897</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19023</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59449</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88974</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32716</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1358</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69714</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7870900000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6425599999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57629</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43633</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49156</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.93892</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.61673</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.25848</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.22183</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25037</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.98123</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69975</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6653300000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.2645</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.5289</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57436</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74263</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4362200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32326</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42082</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.88948</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16792</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.17036</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17481</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.93265</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.92596</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14973</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15747</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14993</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15666</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19642</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.46529</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15627</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16145</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44297</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34814</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5347799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46611</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20338</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25042</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24411</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24273</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24527</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35957</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.42141</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12029</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.24476</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25332</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69817</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5260199999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24309</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28205</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6575299999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76551</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45193</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3444</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21947</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.16966</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64013</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60829</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59615</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46476</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.66465</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47225</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82235</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.55616</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42936</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35965</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48882</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53616</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40718</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55684</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49755</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44846</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.80252</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46678</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5162599999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6502599999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.20944</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49202</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43868</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50801</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51219</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54643</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69924</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7305</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.5205599999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.64506</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80983</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5902500000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52698</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83954</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77915</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62727</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67763</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47604</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47032</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55543</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20642</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11303</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.12496</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36451</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22526</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24998</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13904</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25034</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17098</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18312</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23005</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23397</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34899</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.24733</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23227</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23235</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01818</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03258</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10889</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.02117</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03907</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01338</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03687</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03328</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02464</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02239</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.20484</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00147</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04897</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03511</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17599</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.18862</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26033</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25581</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28677</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.11226</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.55157</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.13135</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22132</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25135</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24132</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.22889</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23452</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.25458</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.23593</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21089</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.12866</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.61719</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.58405</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.63025</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.56853</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.14589</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12042</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23192</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17285</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.09512999999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10595</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.05472999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22281</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.08865000000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.01657</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.07890000000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16276</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.09741</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.10611</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02734</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.07873000000000001</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.09129999999999999</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.09007999999999999</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.13547</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32269</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5475399999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54855</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48505</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44588</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14242</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50675</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32845</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6482899999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.6065499999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50507</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26317</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49281</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50339</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.49011</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42333</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.57032</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36845</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48063</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45995</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45599</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42509</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51387</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58525</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5170800000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50881</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54849</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.46442</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7395700000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9031399999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59273</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.59058</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44437</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37301</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25304</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21761</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23353</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.16721</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15158</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07212</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16779</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16479</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06236999999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06194</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07864</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16643</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08383</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06083</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17489</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15589</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.07109</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.27524</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.24238</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.23964</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35618</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86166</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46626</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24208</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.04884</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.06302000000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.09777</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.23448</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.09099</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00349</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04938</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02102</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02732</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.19312</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23546</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.09709000000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.23687</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.50116</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35794</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45737</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22773</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14254</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20296</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22764</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11284</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14809</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00382</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04742</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04683</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04765</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04757</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07775</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03048</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06264</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09583</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.16775</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19287</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.11893</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12257</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05572</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14399</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11612</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23453</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18217</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.23956</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24079</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3639</v>
       </c>
     </row>
   </sheetData>
